--- a/data/nzd0556/nzd0556.xlsx
+++ b/data/nzd0556/nzd0556.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P264"/>
+  <dimension ref="A1:P267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14603,6 +14603,164 @@
         </is>
       </c>
     </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+      <c r="C265" t="n">
+        <v>300.39</v>
+      </c>
+      <c r="D265" t="n">
+        <v>306.16</v>
+      </c>
+      <c r="E265" t="n">
+        <v>309.26</v>
+      </c>
+      <c r="F265" t="n">
+        <v>301.26</v>
+      </c>
+      <c r="G265" t="n">
+        <v>293.07</v>
+      </c>
+      <c r="H265" t="n">
+        <v>280.3</v>
+      </c>
+      <c r="I265" t="n">
+        <v>267.8</v>
+      </c>
+      <c r="J265" t="n">
+        <v>258.74</v>
+      </c>
+      <c r="K265" t="n">
+        <v>264.44</v>
+      </c>
+      <c r="L265" t="n">
+        <v>279.12</v>
+      </c>
+      <c r="M265" t="n">
+        <v>301.19</v>
+      </c>
+      <c r="N265" t="n">
+        <v>312.57</v>
+      </c>
+      <c r="O265" t="n">
+        <v>324.71</v>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+      <c r="C266" t="n">
+        <v>302.44</v>
+      </c>
+      <c r="D266" t="n">
+        <v>313.34</v>
+      </c>
+      <c r="E266" t="n">
+        <v>313.22</v>
+      </c>
+      <c r="F266" t="n">
+        <v>306.36</v>
+      </c>
+      <c r="G266" t="n">
+        <v>298.89</v>
+      </c>
+      <c r="H266" t="n">
+        <v>290.38</v>
+      </c>
+      <c r="I266" t="n">
+        <v>276.29</v>
+      </c>
+      <c r="J266" t="n">
+        <v>269.88</v>
+      </c>
+      <c r="K266" t="n">
+        <v>268.81</v>
+      </c>
+      <c r="L266" t="n">
+        <v>283.49</v>
+      </c>
+      <c r="M266" t="n">
+        <v>307.46</v>
+      </c>
+      <c r="N266" t="n">
+        <v>314.24</v>
+      </c>
+      <c r="O266" t="n">
+        <v>321.85</v>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>653.05</v>
+      </c>
+      <c r="C267" t="n">
+        <v>302.44</v>
+      </c>
+      <c r="D267" t="n">
+        <v>313.34</v>
+      </c>
+      <c r="E267" t="n">
+        <v>313.22</v>
+      </c>
+      <c r="F267" t="n">
+        <v>306.36</v>
+      </c>
+      <c r="G267" t="n">
+        <v>298.89</v>
+      </c>
+      <c r="H267" t="n">
+        <v>290.38</v>
+      </c>
+      <c r="I267" t="n">
+        <v>276.29</v>
+      </c>
+      <c r="J267" t="n">
+        <v>269.88</v>
+      </c>
+      <c r="K267" t="n">
+        <v>268.81</v>
+      </c>
+      <c r="L267" t="n">
+        <v>283.49</v>
+      </c>
+      <c r="M267" t="n">
+        <v>307.46</v>
+      </c>
+      <c r="N267" t="n">
+        <v>314.24</v>
+      </c>
+      <c r="O267" t="n">
+        <v>321.85</v>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14614,7 +14772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B286"/>
+  <dimension ref="A1:B289"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17477,6 +17635,36 @@
       </c>
       <c r="B286" t="n">
         <v>-0.36</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B289" t="n">
+        <v>0.62</v>
       </c>
     </row>
   </sheetData>
@@ -17645,28 +17833,28 @@
         <v>0.0247</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7065537453506274</v>
+        <v>0.9731735416461068</v>
       </c>
       <c r="J2" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K2" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03927655735632452</v>
+        <v>0.04497465922316013</v>
       </c>
       <c r="M2" t="n">
-        <v>18.23965729045257</v>
+        <v>19.6619610484297</v>
       </c>
       <c r="N2" t="n">
-        <v>673.1442715682609</v>
+        <v>1113.94633663831</v>
       </c>
       <c r="O2" t="n">
-        <v>25.94502402327392</v>
+        <v>33.37583462084971</v>
       </c>
       <c r="P2" t="n">
-        <v>300.500596751472</v>
+        <v>297.694264859352</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17723,28 +17911,28 @@
         <v>0.0356</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4765122881524448</v>
+        <v>-0.4729178396659087</v>
       </c>
       <c r="J3" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K3" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00919564399349182</v>
+        <v>0.009301285198710652</v>
       </c>
       <c r="M3" t="n">
-        <v>21.22600779470594</v>
+        <v>20.97770317438546</v>
       </c>
       <c r="N3" t="n">
-        <v>1348.095901424911</v>
+        <v>1332.085104903966</v>
       </c>
       <c r="O3" t="n">
-        <v>36.71642549901761</v>
+        <v>36.49774109316857</v>
       </c>
       <c r="P3" t="n">
-        <v>312.8644997642771</v>
+        <v>312.8270836892892</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17801,28 +17989,28 @@
         <v>0.0432</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7905553871247628</v>
+        <v>0.7664764154662562</v>
       </c>
       <c r="J4" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K4" t="n">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="L4" t="n">
-        <v>0.188033193055325</v>
+        <v>0.1813124868539588</v>
       </c>
       <c r="M4" t="n">
-        <v>9.690810591199023</v>
+        <v>9.705937495025198</v>
       </c>
       <c r="N4" t="n">
-        <v>147.9053359750986</v>
+        <v>147.5450394904547</v>
       </c>
       <c r="O4" t="n">
-        <v>12.16163377080146</v>
+        <v>12.14681190644091</v>
       </c>
       <c r="P4" t="n">
-        <v>300.4357583988782</v>
+        <v>300.6855427903391</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -17879,28 +18067,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6720065774453431</v>
+        <v>0.6662584910369921</v>
       </c>
       <c r="J5" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K5" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1572879173884055</v>
+        <v>0.1583889146944749</v>
       </c>
       <c r="M5" t="n">
-        <v>8.808321958361606</v>
+        <v>8.738872909021932</v>
       </c>
       <c r="N5" t="n">
-        <v>133.5175114725471</v>
+        <v>132.0974624191293</v>
       </c>
       <c r="O5" t="n">
-        <v>11.55497777897245</v>
+        <v>11.49336601780041</v>
       </c>
       <c r="P5" t="n">
-        <v>296.591473922334</v>
+        <v>296.6507253368761</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -17957,28 +18145,28 @@
         <v>0.0617</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5961416253586899</v>
+        <v>0.5910245864819199</v>
       </c>
       <c r="J6" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K6" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1904656901286547</v>
+        <v>0.1916214771070602</v>
       </c>
       <c r="M6" t="n">
-        <v>6.858428160157509</v>
+        <v>6.811806728371403</v>
       </c>
       <c r="N6" t="n">
-        <v>84.52100579247293</v>
+        <v>83.68161576886943</v>
       </c>
       <c r="O6" t="n">
-        <v>9.193530648911382</v>
+        <v>9.147765616196637</v>
       </c>
       <c r="P6" t="n">
-        <v>291.1179268804374</v>
+        <v>291.1700266670521</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18035,28 +18223,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2820036593094096</v>
+        <v>0.2892949441054624</v>
       </c>
       <c r="J7" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K7" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05070908156947029</v>
+        <v>0.05443391639787964</v>
       </c>
       <c r="M7" t="n">
-        <v>6.936822543647738</v>
+        <v>6.895667595340595</v>
       </c>
       <c r="N7" t="n">
-        <v>83.30485745432283</v>
+        <v>82.55670863593107</v>
       </c>
       <c r="O7" t="n">
-        <v>9.127149470361644</v>
+        <v>9.086072233695431</v>
       </c>
       <c r="P7" t="n">
-        <v>286.2528110033485</v>
+        <v>286.1784145934057</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18113,28 +18301,28 @@
         <v>0.0479</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0979337352084237</v>
+        <v>0.1048376376976094</v>
       </c>
       <c r="J8" t="n">
+        <v>266</v>
+      </c>
+      <c r="K8" t="n">
         <v>263</v>
       </c>
-      <c r="K8" t="n">
-        <v>260</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.008396696499956668</v>
+        <v>0.009806892398193878</v>
       </c>
       <c r="M8" t="n">
-        <v>6.211359054552558</v>
+        <v>6.200146672379866</v>
       </c>
       <c r="N8" t="n">
-        <v>63.51204797320425</v>
+        <v>63.14632539666353</v>
       </c>
       <c r="O8" t="n">
-        <v>7.969444646473445</v>
+        <v>7.946466220696061</v>
       </c>
       <c r="P8" t="n">
-        <v>281.3765734709006</v>
+        <v>281.3060683858296</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18191,28 +18379,28 @@
         <v>0.059</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04302965818901148</v>
+        <v>-0.03773426765040159</v>
       </c>
       <c r="J9" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K9" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002036709914519985</v>
+        <v>0.001600784847312964</v>
       </c>
       <c r="M9" t="n">
-        <v>5.621051510831001</v>
+        <v>5.607388950481304</v>
       </c>
       <c r="N9" t="n">
-        <v>50.76547308037176</v>
+        <v>50.43029352869998</v>
       </c>
       <c r="O9" t="n">
-        <v>7.124989338965481</v>
+        <v>7.101428977938172</v>
       </c>
       <c r="P9" t="n">
-        <v>272.2675683850624</v>
+        <v>272.2134846526513</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18269,28 +18457,28 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1180619422358447</v>
+        <v>-0.1122300678669814</v>
       </c>
       <c r="J10" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K10" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01433088859501419</v>
+        <v>0.01321226917398088</v>
       </c>
       <c r="M10" t="n">
-        <v>5.586556226513011</v>
+        <v>5.584398499928714</v>
       </c>
       <c r="N10" t="n">
-        <v>53.5913565332448</v>
+        <v>53.36845920794376</v>
       </c>
       <c r="O10" t="n">
-        <v>7.320611759494202</v>
+        <v>7.305371941793502</v>
       </c>
       <c r="P10" t="n">
-        <v>266.7342208663304</v>
+        <v>266.6745917956471</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18347,28 +18535,28 @@
         <v>0.0497</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.241584404132854</v>
+        <v>-0.2326610884624204</v>
       </c>
       <c r="J11" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K11" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0479507389930629</v>
+        <v>0.04560982035226469</v>
       </c>
       <c r="M11" t="n">
-        <v>6.453575542464483</v>
+        <v>6.424684764079963</v>
       </c>
       <c r="N11" t="n">
-        <v>64.77669416421277</v>
+        <v>64.25915298884465</v>
       </c>
       <c r="O11" t="n">
-        <v>8.048396993452346</v>
+        <v>8.016180698365316</v>
       </c>
       <c r="P11" t="n">
-        <v>269.8222265303912</v>
+        <v>269.7311436571751</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -18425,28 +18613,28 @@
         <v>0.1044</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3077667365705134</v>
+        <v>-0.2893077730979283</v>
       </c>
       <c r="J12" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K12" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1036280499858607</v>
+        <v>0.09346711610412795</v>
       </c>
       <c r="M12" t="n">
-        <v>5.280367882237996</v>
+        <v>5.323409774321175</v>
       </c>
       <c r="N12" t="n">
-        <v>45.75791506772524</v>
+        <v>46.0145886985011</v>
       </c>
       <c r="O12" t="n">
-        <v>6.764459702572352</v>
+        <v>6.783405390989182</v>
       </c>
       <c r="P12" t="n">
-        <v>282.0286838796786</v>
+        <v>281.8405043395257</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -18503,28 +18691,28 @@
         <v>0.056</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5124627385390897</v>
+        <v>-0.4799901651037621</v>
       </c>
       <c r="J13" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K13" t="n">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1889286945861876</v>
+        <v>0.1681467570978713</v>
       </c>
       <c r="M13" t="n">
-        <v>6.589444526701107</v>
+        <v>6.670356306453401</v>
       </c>
       <c r="N13" t="n">
-        <v>63.02350834016322</v>
+        <v>64.66105426198916</v>
       </c>
       <c r="O13" t="n">
-        <v>7.93873468130553</v>
+        <v>8.041209751149959</v>
       </c>
       <c r="P13" t="n">
-        <v>304.6053325280911</v>
+        <v>304.2739940665056</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -18581,28 +18769,28 @@
         <v>0.0689</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6004672881772294</v>
+        <v>-0.5800579713327172</v>
       </c>
       <c r="J14" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K14" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2063023516691476</v>
+        <v>0.1974954659390691</v>
       </c>
       <c r="M14" t="n">
-        <v>7.044568373210177</v>
+        <v>7.070767770794521</v>
       </c>
       <c r="N14" t="n">
-        <v>78.00217125976417</v>
+        <v>78.02647193327577</v>
       </c>
       <c r="O14" t="n">
-        <v>8.831883788850721</v>
+        <v>8.833259417297546</v>
       </c>
       <c r="P14" t="n">
-        <v>320.5166093401621</v>
+        <v>320.3098245079328</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -18659,28 +18847,28 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4428693830293435</v>
+        <v>-0.4243978968979167</v>
       </c>
       <c r="J15" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="K15" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09692715163023413</v>
+        <v>0.09125896985106874</v>
       </c>
       <c r="M15" t="n">
-        <v>7.919892546587803</v>
+        <v>7.915366382334844</v>
       </c>
       <c r="N15" t="n">
-        <v>102.8574772546345</v>
+        <v>102.4505786143572</v>
       </c>
       <c r="O15" t="n">
-        <v>10.14186754274746</v>
+        <v>10.12178732311429</v>
       </c>
       <c r="P15" t="n">
-        <v>326.3211322266811</v>
+        <v>326.1338637254752</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -18718,7 +18906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P264"/>
+  <dimension ref="A1:P267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40145,6 +40333,244 @@
         </is>
       </c>
     </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>-46.62444775147935,169.26839182473964</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>-46.62492977593121,169.26782209394366</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>-46.62539462202521,169.2672280226453</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>-46.62578806230017,169.26653275935232</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-46.62618027612756,169.26583576379352</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-46.626543023805006,169.26509701501058</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-46.6269075037073,169.2643607275412</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>-46.62729410788608,169.26365580027962</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>-46.62777565656361,169.26308543079307</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>-46.62831496910627,169.26259692727282</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>-46.628901817868766,169.26217579578724</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>-46.62941989635773,169.26165720995107</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>-46.62994286089974,169.26114555342775</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>-46.624460938203335,169.2684105132408</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>-46.62497596182898,169.26788754953853</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>-46.62542009515641,169.26726412358693</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>-46.625820868802265,169.26657925299938</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-46.626217714361935,169.26588882125608</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-46.62660786569367,169.2651889082979</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-46.6269621179209,169.26443812566563</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-46.62736576937107,169.26375735684394</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>-46.62780376807611,169.2631252695101</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>-46.6283430807226,169.26263676620746</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>-46.628942152040864,169.26223295642296</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>-46.62943063931712,169.2616724346171</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>-46.62992446270048,169.26111947993488</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:06+00:00</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>-46.626271288531086,169.27222925342272</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>-46.624460938203335,169.2684105132408</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>-46.62497596182898,169.26788754953853</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>-46.62542009515641,169.26726412358693</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>-46.625820868802265,169.26657925299938</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>-46.626217714361935,169.26588882125608</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>-46.62660786569367,169.2651889082979</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>-46.6269621179209,169.26443812566563</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>-46.62736576937107,169.26375735684394</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>-46.62780376807611,169.2631252695101</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>-46.6283430807226,169.26263676620746</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>-46.628942152040864,169.26223295642296</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>-46.62943063931712,169.2616724346171</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>-46.62992446270048,169.26111947993488</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0556/nzd0556.xlsx
+++ b/data/nzd0556/nzd0556.xlsx
@@ -14710,50 +14710,50 @@
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>2026-05-23 22:20:06+00:00</t>
+          <t>2026-06-08 22:20:03+00:00</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>653.05</v>
+        <v>205.04</v>
       </c>
       <c r="C267" t="n">
-        <v>302.44</v>
+        <v>288.96</v>
       </c>
       <c r="D267" t="n">
-        <v>313.34</v>
+        <v>302.71</v>
       </c>
       <c r="E267" t="n">
-        <v>313.22</v>
+        <v>300.44</v>
       </c>
       <c r="F267" t="n">
-        <v>306.36</v>
+        <v>297.13</v>
       </c>
       <c r="G267" t="n">
-        <v>298.89</v>
+        <v>288.22</v>
       </c>
       <c r="H267" t="n">
-        <v>290.38</v>
+        <v>277.96</v>
       </c>
       <c r="I267" t="n">
-        <v>276.29</v>
+        <v>268.75</v>
       </c>
       <c r="J267" t="n">
-        <v>269.88</v>
+        <v>258.88</v>
       </c>
       <c r="K267" t="n">
-        <v>268.81</v>
+        <v>261.55</v>
       </c>
       <c r="L267" t="n">
-        <v>283.49</v>
+        <v>273.48</v>
       </c>
       <c r="M267" t="n">
-        <v>307.46</v>
+        <v>298.54</v>
       </c>
       <c r="N267" t="n">
-        <v>314.24</v>
+        <v>305.83</v>
       </c>
       <c r="O267" t="n">
-        <v>321.85</v>
+        <v>311.95</v>
       </c>
       <c r="P267" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B289"/>
+  <dimension ref="A1:B290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17665,6 +17665,16 @@
       </c>
       <c r="B289" t="n">
         <v>0.62</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B290" t="n">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -17833,7 +17843,7 @@
         <v>0.0247</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9731735416461068</v>
+        <v>0.6149409506490147</v>
       </c>
       <c r="J2" t="n">
         <v>266</v>
@@ -17842,19 +17852,19 @@
         <v>248</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04497465922316013</v>
+        <v>0.02818066619734416</v>
       </c>
       <c r="M2" t="n">
-        <v>19.6619610484297</v>
+        <v>18.60807934896866</v>
       </c>
       <c r="N2" t="n">
-        <v>1113.94633663831</v>
+        <v>722.3841857749778</v>
       </c>
       <c r="O2" t="n">
-        <v>33.37583462084971</v>
+        <v>26.87720569134704</v>
       </c>
       <c r="P2" t="n">
-        <v>297.694264859352</v>
+        <v>301.4666914013754</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -17911,7 +17921,7 @@
         <v>0.0356</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4729178396659087</v>
+        <v>-0.4835355437692835</v>
       </c>
       <c r="J3" t="n">
         <v>266</v>
@@ -17920,19 +17930,19 @@
         <v>252</v>
       </c>
       <c r="L3" t="n">
-        <v>0.009301285198710652</v>
+        <v>0.009716735843070978</v>
       </c>
       <c r="M3" t="n">
-        <v>20.97770317438546</v>
+        <v>21.0531649521855</v>
       </c>
       <c r="N3" t="n">
-        <v>1332.085104903966</v>
+        <v>1332.563109117069</v>
       </c>
       <c r="O3" t="n">
-        <v>36.49774109316857</v>
+        <v>36.50428891400391</v>
       </c>
       <c r="P3" t="n">
-        <v>312.8270836892892</v>
+        <v>312.9378431369125</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -17989,7 +17999,7 @@
         <v>0.0432</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7664764154662562</v>
+        <v>0.7582120204430556</v>
       </c>
       <c r="J4" t="n">
         <v>266</v>
@@ -17998,19 +18008,19 @@
         <v>261</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1813124868539588</v>
+        <v>0.1770820833540563</v>
       </c>
       <c r="M4" t="n">
-        <v>9.705937495025198</v>
+        <v>9.749550637963234</v>
       </c>
       <c r="N4" t="n">
-        <v>147.5450394904547</v>
+        <v>148.6035409163152</v>
       </c>
       <c r="O4" t="n">
-        <v>12.14681190644091</v>
+        <v>12.19030520193466</v>
       </c>
       <c r="P4" t="n">
-        <v>300.6855427903391</v>
+        <v>300.7716857448798</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18067,7 +18077,7 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6662584910369921</v>
+        <v>0.6564212108521301</v>
       </c>
       <c r="J5" t="n">
         <v>266</v>
@@ -18076,19 +18086,19 @@
         <v>262</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1583889146944749</v>
+        <v>0.1537563567556404</v>
       </c>
       <c r="M5" t="n">
-        <v>8.738872909021932</v>
+        <v>8.792201618283553</v>
       </c>
       <c r="N5" t="n">
-        <v>132.0974624191293</v>
+        <v>132.8247548317157</v>
       </c>
       <c r="O5" t="n">
-        <v>11.49336601780041</v>
+        <v>11.52496224860263</v>
       </c>
       <c r="P5" t="n">
-        <v>296.6507253368761</v>
+        <v>296.7525444360428</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18145,7 +18155,7 @@
         <v>0.0617</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5910245864819199</v>
+        <v>0.5840081491699802</v>
       </c>
       <c r="J6" t="n">
         <v>266</v>
@@ -18154,19 +18164,19 @@
         <v>264</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1916214771070602</v>
+        <v>0.1873127454926922</v>
       </c>
       <c r="M6" t="n">
-        <v>6.811806728371403</v>
+        <v>6.85462011835543</v>
       </c>
       <c r="N6" t="n">
-        <v>83.68161576886943</v>
+        <v>84.03711033406088</v>
       </c>
       <c r="O6" t="n">
-        <v>9.147765616196637</v>
+        <v>9.1671757010576</v>
       </c>
       <c r="P6" t="n">
-        <v>291.1700266670521</v>
+        <v>291.2417825252533</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18223,7 +18233,7 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2892949441054624</v>
+        <v>0.2812064325100506</v>
       </c>
       <c r="J7" t="n">
         <v>266</v>
@@ -18232,19 +18242,19 @@
         <v>264</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05443391639787964</v>
+        <v>0.05157891462812059</v>
       </c>
       <c r="M7" t="n">
-        <v>6.895667595340595</v>
+        <v>6.901323090088866</v>
       </c>
       <c r="N7" t="n">
-        <v>82.55670863593107</v>
+        <v>82.57653967645759</v>
       </c>
       <c r="O7" t="n">
-        <v>9.086072233695431</v>
+        <v>9.087163456021774</v>
       </c>
       <c r="P7" t="n">
-        <v>286.1784145934057</v>
+        <v>286.2610524365287</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18301,7 +18311,7 @@
         <v>0.0479</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1048376376976094</v>
+        <v>0.09543521548964279</v>
       </c>
       <c r="J8" t="n">
         <v>266</v>
@@ -18310,19 +18320,19 @@
         <v>263</v>
       </c>
       <c r="L8" t="n">
-        <v>0.009806892398193878</v>
+        <v>0.00814274181217034</v>
       </c>
       <c r="M8" t="n">
-        <v>6.200146672379866</v>
+        <v>6.202470041349041</v>
       </c>
       <c r="N8" t="n">
-        <v>63.14632539666353</v>
+        <v>63.13203219839978</v>
       </c>
       <c r="O8" t="n">
-        <v>7.946466220696061</v>
+        <v>7.945566826753129</v>
       </c>
       <c r="P8" t="n">
-        <v>281.3060683858296</v>
+        <v>281.4021311430816</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18379,7 +18389,7 @@
         <v>0.059</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.03773426765040159</v>
+        <v>-0.04343829722438696</v>
       </c>
       <c r="J9" t="n">
         <v>266</v>
@@ -18388,19 +18398,19 @@
         <v>264</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001600784847312964</v>
+        <v>0.002123609829059125</v>
       </c>
       <c r="M9" t="n">
-        <v>5.607388950481304</v>
+        <v>5.598414712316654</v>
       </c>
       <c r="N9" t="n">
-        <v>50.43029352869998</v>
+        <v>50.35293413680555</v>
       </c>
       <c r="O9" t="n">
-        <v>7.101428977938172</v>
+        <v>7.095980139262339</v>
       </c>
       <c r="P9" t="n">
-        <v>272.2134846526513</v>
+        <v>272.271738647943</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18457,7 +18467,7 @@
         <v>0.07539999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1122300678669814</v>
+        <v>-0.1205581658665554</v>
       </c>
       <c r="J10" t="n">
         <v>266</v>
@@ -18466,19 +18476,19 @@
         <v>264</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01321226917398088</v>
+        <v>0.01523367283794996</v>
       </c>
       <c r="M10" t="n">
-        <v>5.584398499928714</v>
+        <v>5.584878869107106</v>
       </c>
       <c r="N10" t="n">
-        <v>53.36845920794376</v>
+        <v>53.30531697921834</v>
       </c>
       <c r="O10" t="n">
-        <v>7.305371941793502</v>
+        <v>7.301049032790996</v>
       </c>
       <c r="P10" t="n">
-        <v>266.6745917956471</v>
+        <v>266.7597253853932</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18535,7 +18545,7 @@
         <v>0.0497</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2326610884624204</v>
+        <v>-0.2381502156781714</v>
       </c>
       <c r="J11" t="n">
         <v>266</v>
@@ -18544,19 +18554,19 @@
         <v>264</v>
       </c>
       <c r="L11" t="n">
-        <v>0.04560982035226469</v>
+        <v>0.04775176389340785</v>
       </c>
       <c r="M11" t="n">
-        <v>6.424684764079963</v>
+        <v>6.411836955478245</v>
       </c>
       <c r="N11" t="n">
-        <v>64.25915298884465</v>
+        <v>64.16695297401384</v>
       </c>
       <c r="O11" t="n">
-        <v>8.016180698365316</v>
+        <v>8.010427764733532</v>
       </c>
       <c r="P11" t="n">
-        <v>269.7311436571751</v>
+        <v>269.7872387661897</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -18613,7 +18623,7 @@
         <v>0.1044</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2893077730979283</v>
+        <v>-0.2968566460908585</v>
       </c>
       <c r="J12" t="n">
         <v>266</v>
@@ -18622,19 +18632,19 @@
         <v>265</v>
       </c>
       <c r="L12" t="n">
-        <v>0.09346711610412795</v>
+        <v>0.09857013667693415</v>
       </c>
       <c r="M12" t="n">
-        <v>5.323409774321175</v>
+        <v>5.285445707967176</v>
       </c>
       <c r="N12" t="n">
-        <v>46.0145886985011</v>
+        <v>45.68351896793306</v>
       </c>
       <c r="O12" t="n">
-        <v>6.783405390989182</v>
+        <v>6.758958423302592</v>
       </c>
       <c r="P12" t="n">
-        <v>281.8405043395257</v>
+        <v>281.9175446053467</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -18691,7 +18701,7 @@
         <v>0.056</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4799901651037621</v>
+        <v>-0.486694336375965</v>
       </c>
       <c r="J13" t="n">
         <v>266</v>
@@ -18700,19 +18710,19 @@
         <v>264</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1681467570978713</v>
+        <v>0.1738016145964324</v>
       </c>
       <c r="M13" t="n">
-        <v>6.670356306453401</v>
+        <v>6.638103011086447</v>
       </c>
       <c r="N13" t="n">
-        <v>64.66105426198916</v>
+        <v>63.88395871514274</v>
       </c>
       <c r="O13" t="n">
-        <v>8.041209751149959</v>
+        <v>7.992744129217621</v>
       </c>
       <c r="P13" t="n">
-        <v>304.2739940665056</v>
+        <v>304.3423674049559</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -18769,7 +18779,7 @@
         <v>0.0689</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5800579713327172</v>
+        <v>-0.5863412913152793</v>
       </c>
       <c r="J14" t="n">
         <v>266</v>
@@ -18778,19 +18788,19 @@
         <v>266</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1974954659390691</v>
+        <v>0.2016179581396551</v>
       </c>
       <c r="M14" t="n">
-        <v>7.070767770794521</v>
+        <v>7.037949971677977</v>
       </c>
       <c r="N14" t="n">
-        <v>78.02647193327577</v>
+        <v>77.69980385765714</v>
       </c>
       <c r="O14" t="n">
-        <v>8.833259417297546</v>
+        <v>8.81474922261871</v>
       </c>
       <c r="P14" t="n">
-        <v>320.3098245079328</v>
+        <v>320.373545745377</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -18847,7 +18857,7 @@
         <v>0.07870000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4243978968979167</v>
+        <v>-0.4318256956648292</v>
       </c>
       <c r="J15" t="n">
         <v>266</v>
@@ -18856,19 +18866,19 @@
         <v>265</v>
       </c>
       <c r="L15" t="n">
-        <v>0.09125896985106874</v>
+        <v>0.09431396297911943</v>
       </c>
       <c r="M15" t="n">
-        <v>7.915366382334844</v>
+        <v>7.902205104896938</v>
       </c>
       <c r="N15" t="n">
-        <v>102.4505786143572</v>
+        <v>102.2941187524644</v>
       </c>
       <c r="O15" t="n">
-        <v>10.12178732311429</v>
+        <v>10.11405550471543</v>
       </c>
       <c r="P15" t="n">
-        <v>326.1338637254752</v>
+        <v>326.209318998158</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -40492,77 +40502,77 @@
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>2026-05-23 22:20:06+00:00</t>
+          <t>2026-06-08 22:20:03+00:00</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>-46.626271288531086,169.27222925342272</t>
+          <t>-46.62338949597238,169.2681449255029</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>-46.624460938203335,169.2684105132408</t>
+          <t>-46.6243742274008,169.26828762511664</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>-46.62497596182898,169.26788754953853</t>
+          <t>-46.6249075835307,169.26779064247881</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>-46.62542009515641,169.26726412358693</t>
+          <t>-46.625337886377004,169.26714761612453</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>-46.625820868802265,169.26657925299938</t>
+          <t>-46.62576149545333,169.26649510865582</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>-46.626217714361935,169.26588882125608</t>
+          <t>-46.626149077581566,169.2657915492973</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>-46.62660786569367,169.2651889082979</t>
+          <t>-46.62652797121396,169.26507568267172</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>-46.6269621179209,169.26443812566563</t>
+          <t>-46.626913614840795,169.264369388101</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>-46.62736576937107,169.26375735684394</t>
+          <t>-46.62729500847977,169.2636570765723</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>-46.62780376807611,169.2631252695101</t>
+          <t>-46.627757065647835,169.2630590843873</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>-46.6283430807226,169.26263676620746</t>
+          <t>-46.62827868773355,169.26254551049374</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>-46.628942152040864,169.26223295642296</t>
+          <t>-46.62888477072271,169.26215163701139</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>-46.62943063931712,169.2616724346171</t>
+          <t>-46.62937653852651,169.2615957643541</t>
         </is>
       </c>
       <c r="O267" t="inlineStr">
         <is>
-          <t>-46.62992446270048,169.26111947993488</t>
+          <t>-46.62986077658378,169.26102922567304</t>
         </is>
       </c>
       <c r="P267" t="inlineStr">
